--- a/dcf/WMB.xlsx
+++ b/dcf/WMB.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.04710823157291531</v>
+        <v>0.04719333787793438</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.05210823157291531</v>
+        <v>0.05219333787793438</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.05710823157291531</v>
+        <v>0.05719333787793438</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.06210823157291531</v>
+        <v>0.06219333787793438</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.06710823157291532</v>
+        <v>0.06719333787793438</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.07210823157291531</v>
+        <v>0.07219333787793437</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.07710823157291531</v>
+        <v>0.07719333787793438</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>60.62310506423526</v>
+        <v>60.55919300910117</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>56.96003742295225</v>
+        <v>56.8992736796801</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>53.47695158712456</v>
+        <v>53.41916539155121</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>50.16410884838897</v>
+        <v>50.1091394956515</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>47.01234284523315</v>
+        <v>46.96003905192082</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>44.01302335406403</v>
+        <v>43.96324266361854</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>41.15802252983635</v>
+        <v>41.11063075808122</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>67.76878654739809</v>
+        <v>67.69906925874247</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>63.7733012441841</v>
+        <v>63.7070286207604</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>59.97472921289752</v>
+        <v>59.91171406309637</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>56.36239530423677</v>
+        <v>56.30246147768494</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>52.92625256590924</v>
+        <v>52.8692342527028</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>49.65684246295806</v>
+        <v>49.6025835404435</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>46.54525779113276</v>
+        <v>46.49361121480518</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>74.91446803056093</v>
+        <v>74.83894550838374</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>70.58656506541594</v>
+        <v>70.51478356184069</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>66.47250683867047</v>
+        <v>66.40426273464152</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>62.56068176008454</v>
+        <v>62.49578345971838</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>58.84016228658533</v>
+        <v>58.7784294534848</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>55.30066157185208</v>
+        <v>55.24192441726846</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>51.93249305242916</v>
+        <v>51.87659167152914</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>82.06014951372377</v>
+        <v>81.97882175802503</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>77.39982888664777</v>
+        <v>77.32253850292098</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>72.97028446444344</v>
+        <v>72.89681140618666</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>68.75896821593233</v>
+        <v>68.68910544175179</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>64.75407200726141</v>
+        <v>64.68762465426677</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>60.94448068074612</v>
+        <v>60.88126529409342</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>57.31972831372556</v>
+        <v>57.25957212825309</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>89.2058309968866</v>
+        <v>89.11869800766631</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>84.21309270787962</v>
+        <v>84.13029344400125</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>79.46806209021641</v>
+        <v>79.38936007773182</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>74.95725467178012</v>
+        <v>74.88242742378523</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>70.6679817279375</v>
+        <v>70.59681985504875</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>66.58829978964013</v>
+        <v>66.52060617091838</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>62.70696357502197</v>
+        <v>62.64255258497705</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>96.35151248004944</v>
+        <v>96.25857425730763</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>91.02635652911147</v>
+        <v>90.93804838508156</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>85.96583971598936</v>
+        <v>85.88190874927697</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>81.15554112762791</v>
+        <v>81.07574940581867</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>76.5818914486136</v>
+        <v>76.50601505583074</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>72.23211889853418</v>
+        <v>72.15994704774336</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>68.09419883631837</v>
+        <v>68.02553304170102</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>103.4971939632123</v>
+        <v>103.3984505069489</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>97.83962035034331</v>
+        <v>97.74580332616185</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>92.46361734176232</v>
+        <v>92.37445742082211</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>87.35382758347571</v>
+        <v>87.26907138785211</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>82.49580116928971</v>
+        <v>82.41521025661272</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>77.8759380074282</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>73.48143409761478</v>
+        <v>77.79928792456832</v>
+      </c>
+      <c r="H11" s="53" t="n">
+        <v>73.40851349842498</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>73.13999938964844</v>
+        <v>74.03500366210938</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.06210823157291531</v>
+        <v>0.06219333787793438</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.9851698201133955</v>
+        <v>0.9851539825873225</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>73.13999938964844</v>
+        <v>74.03500366210938</v>
       </c>
     </row>
     <row r="49">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>68.75896821593233</v>
+        <v>68.68910544175179</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>107.2837449456687</v>
+        <v>107.1843653435302</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>39.73513763313718</v>
+        <v>39.68735000596287</v>
       </c>
     </row>
     <row r="59">
